--- a/Analisis/2.PCA_AED/datosLimpio.xlsx
+++ b/Analisis/2.PCA_AED/datosLimpio.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manuelrocamoravalenti/Desktop/TFG/Analisis/2.PCA_AED/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/sotacam_upv_edu_es/Documents/TesisTreballs/TFG_ManuelRocamora/TFG_ManuelRocamora/Analisis/2.PCA_AED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8FFE88-C4CA-D744-A451-DE785CC286F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{7B8FFE88-C4CA-D744-A451-DE785CC286F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB320019-DCCF-FA45-8498-3229303065B6}"/>
   <bookViews>
-    <workbookView xWindow="40440" yWindow="-1040" windowWidth="30220" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41600" yWindow="920" windowWidth="30220" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -338,7 +338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +350,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -387,15 +395,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -786,64 +797,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>103</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -864,7 +875,7 @@
       <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -885,7 +896,7 @@
       <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="AI1" s="1" t="s">
@@ -906,7 +917,7 @@
       <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="AP1" s="1" t="s">
@@ -927,7 +938,7 @@
       <c r="AU1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AW1" s="1" t="s">
@@ -948,7 +959,7 @@
       <c r="BB1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="3" t="s">
         <v>53</v>
       </c>
       <c r="BD1" s="1" t="s">
@@ -969,7 +980,7 @@
       <c r="BI1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>60</v>
       </c>
       <c r="BK1" s="1" t="s">
@@ -990,7 +1001,7 @@
       <c r="BP1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>67</v>
       </c>
       <c r="BR1" s="1" t="s">
@@ -1011,7 +1022,7 @@
       <c r="BW1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" s="3" t="s">
         <v>74</v>
       </c>
       <c r="BY1" s="1" t="s">
@@ -1032,7 +1043,7 @@
       <c r="CD1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" s="3" t="s">
         <v>81</v>
       </c>
       <c r="CF1" s="1" t="s">
@@ -1053,7 +1064,7 @@
       <c r="CK1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CL1" s="3" t="s">
         <v>88</v>
       </c>
       <c r="CM1" s="1" t="s">
